--- a/Test-Cases/Notes_Test_Cases.xlsx
+++ b/Test-Cases/Notes_Test_Cases.xlsx
@@ -9,10 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Test_Cases" sheetId="1" r:id="rId1"/>
+    <sheet name="AI_Test_Cases" sheetId="2" r:id="rId2"/>
+    <sheet name="Bug_reporting" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -24,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="229">
   <si>
     <t>Module</t>
   </si>
@@ -294,14 +296,6 @@
 Description: Updated Work Testing</t>
   </si>
   <si>
-    <t>Category: Professional
-Title: Professional Task
-Description: Perform Professional Testing</t>
-  </si>
-  <si>
-    <t>Note should appear under Professional and All categories only.</t>
-  </si>
-  <si>
     <t>TC-3.1</t>
   </si>
   <si>
@@ -336,17 +330,6 @@
 Description: Perform Automation Testing using Cypress</t>
   </si>
   <si>
-    <t>Edit note in Professional</t>
-  </si>
-  <si>
-    <t>Note exists in Professional category</t>
-  </si>
-  <si>
-    <t>Category: Professional
-Title: Professional Task Updated
-Description: Updated Professional Testing</t>
-  </si>
-  <si>
     <t>TC-4.1</t>
   </si>
   <si>
@@ -374,16 +357,6 @@
   </si>
   <si>
     <t>Note should be removed from Work and All categories.</t>
-  </si>
-  <si>
-    <t>Delete note in Professional</t>
-  </si>
-  <si>
-    <t>Category: Professional
-Title: Professional Task Updated</t>
-  </si>
-  <si>
-    <t>Note should be removed from Professional and All categories.</t>
   </si>
   <si>
     <t>TC-5.1</t>
@@ -420,17 +393,6 @@
     <t>1. Launch the browser.
 2. Navigate to the application URL.
 3. Login with valid credentials.
-4. Click on “Add Note”.
-5. Select Category: Professional.
-6. Enter Title: Professional Task.
-7. Enter Description: Perform Professional Testing.
-8. Click Save.
-9. Verify note appears under Professional and All categories.</t>
-  </si>
-  <si>
-    <t>1. Launch the browser.
-2. Navigate to the application URL.
-3. Login with valid credentials.
 4. Navigate to Personal category.
 5. Click Edit on existing note.
 6. Update Title and Description.
@@ -451,16 +413,6 @@
     <t>1. Launch the browser.
 2. Navigate to the application URL.
 3. Login with valid credentials.
-4. Navigate to Professional category.
-5. Click Edit on existing note.
-6. Update Title and Description.
-7. Click Save.
-8. Verify updated note appears in Professional and All categories.</t>
-  </si>
-  <si>
-    <t>1. Launch the browser.
-2. Navigate to the application URL.
-3. Login with valid credentials.
 4. Navigate to Personal category.
 5. Click Delete on existing note.
 6. Confirm deletion.
@@ -475,15 +427,6 @@
 5. Click Delete on existing note.
 6. Confirm deletion.
 7. Verify note is removed from Work and All categories.</t>
-  </si>
-  <si>
-    <t>1. Launch the browser.
-2. Navigate to the application URL.
-3. Login with valid credentials.
-4. Navigate to Professional category.
-5. Click Delete on existing note.
-6. Confirm deletion.
-7. Verify note is removed from Professional and All categories.</t>
   </si>
   <si>
     <t>1. Launch the browser.
@@ -521,6 +464,524 @@
 6. Click on Login.
 7. Verify user is redirected to Dashboard.
 8. Verify Profile and Logout options are visible.</t>
+  </si>
+  <si>
+    <t>Edit note in Home</t>
+  </si>
+  <si>
+    <t>1. Launch the browser.
+2. Navigate to the application URL.
+3. Login with valid credentials.
+4. Navigate to Home category.
+5. Click Edit on existing note.
+6. Update Title and Description.
+7. Click Save.
+8. Verify updated note appears in Home and All categories.</t>
+  </si>
+  <si>
+    <t>Category: Home
+Title: Home Task Updated</t>
+  </si>
+  <si>
+    <t>Note should be removed from Home and All categories.</t>
+  </si>
+  <si>
+    <t>1. Launch the browser.
+2. Navigate to the application URL.
+3. Login with valid credentials.
+4. Navigate to Home category.
+5. Click Delete on existing note.
+6. Confirm deletion.
+7. Verify note is removed from Home and All categories.</t>
+  </si>
+  <si>
+    <t>Note exists in Home category</t>
+  </si>
+  <si>
+    <t>Delete note in Home</t>
+  </si>
+  <si>
+    <t>1. Launch the browser.
+2. Navigate to the application URL.
+3. Login with valid credentials.
+4. Click on “Add Note”.
+5. Select Category: Home
+6. Enter Title: Professional Task.
+7. Enter Description: Perform Home Testing.
+8. Click Save.
+9. Verify note appears under Home and All categories.</t>
+  </si>
+  <si>
+    <t>Category: Home
+Title: Home Task
+Description: Perform Home Testing</t>
+  </si>
+  <si>
+    <t>Note should appear under Home and All categories only.</t>
+  </si>
+  <si>
+    <t>Category: Home
+Title: Home Task remainder
+Description: Updated Home Testing</t>
+  </si>
+  <si>
+    <t>Bug ID</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Precondition</t>
+  </si>
+  <si>
+    <t>Steps to Reproduce</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>CRIT_01</t>
+  </si>
+  <si>
+    <t>Notes – Category Filter</t>
+  </si>
+  <si>
+    <t>Notes from other categories appear in selected category</t>
+  </si>
+  <si>
+    <t>User logged in, multiple notes exist in Home, Work, Personal</t>
+  </si>
+  <si>
+    <t>1. Navigate to Home category.
+2. Observe notes displayed.</t>
+  </si>
+  <si>
+    <t>Only Home notes appear</t>
+  </si>
+  <si>
+    <t>Notes from Work &amp; Personal also appear</t>
+  </si>
+  <si>
+    <t>CRIT_02</t>
+  </si>
+  <si>
+    <t>Notes – Search Filter</t>
+  </si>
+  <si>
+    <t>Search displays notes from all categories, ignoring selection</t>
+  </si>
+  <si>
+    <t>User logged in, multiple notes with overlapping keywords exist</t>
+  </si>
+  <si>
+    <t>1. Select Home category.
+2. Search “New Test”.
+3. Observe results</t>
+  </si>
+  <si>
+    <t>Only notes in Home with exact match appear</t>
+  </si>
+  <si>
+    <t>Notes from Home &amp; Work displayed</t>
+  </si>
+  <si>
+    <t>Notes – Category</t>
+  </si>
+  <si>
+    <t>Category selection dropdown resets after adding note</t>
+  </si>
+  <si>
+    <t>User logged in</t>
+  </si>
+  <si>
+    <t>1. Select Work category.
+2. Add note.
+3. Check category dropdown</t>
+  </si>
+  <si>
+    <t>Dropdown retains last selected category</t>
+  </si>
+  <si>
+    <t>Resets to default</t>
+  </si>
+  <si>
+    <t>Login allows blank email/password</t>
+  </si>
+  <si>
+    <t>Login page accessible</t>
+  </si>
+  <si>
+    <t>1. Leave Email &amp; Password blank.
+2. Click Login</t>
+  </si>
+  <si>
+    <t>Validation message displayed</t>
+  </si>
+  <si>
+    <t>Login button clickable, error inconsistent</t>
+  </si>
+  <si>
+    <t>Registration</t>
+  </si>
+  <si>
+    <t>Registration allows weak password</t>
+  </si>
+  <si>
+    <t>Registration page accessible</t>
+  </si>
+  <si>
+    <t>1. Enter valid Name &amp; Email.
+2. Enter password: “123456”
+3. Click Register</t>
+  </si>
+  <si>
+    <t>Password strength validation</t>
+  </si>
+  <si>
+    <t>Registration succeeds with weak password</t>
+  </si>
+  <si>
+    <t>BUG_1</t>
+  </si>
+  <si>
+    <t>BUG_2</t>
+  </si>
+  <si>
+    <t>BUG_3</t>
+  </si>
+  <si>
+    <t>Register with valid credentials</t>
+  </si>
+  <si>
+    <t>System should create the user account successfully and redirect the user as per application workflow.</t>
+  </si>
+  <si>
+    <t>Register with already registered email</t>
+  </si>
+  <si>
+    <t>System should display “Email already exists” message and prevent account creation. User remains on registration page.</t>
+  </si>
+  <si>
+    <t>Register with invalid email format</t>
+  </si>
+  <si>
+    <t>System should display email format validation message and block registration.</t>
+  </si>
+  <si>
+    <t>Register with mandatory fields empty</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>System should display required field validation messages and prevent submission.</t>
+  </si>
+  <si>
+    <t>Successful login with valid credentials</t>
+  </si>
+  <si>
+    <t>User should be authenticated successfully and granted access to dashboard.</t>
+  </si>
+  <si>
+    <t>Login with invalid email</t>
+  </si>
+  <si>
+    <t>System should display “Invalid email or password” and deny access.</t>
+  </si>
+  <si>
+    <t>Login with incorrect password</t>
+  </si>
+  <si>
+    <t>System should display authentication error and restrict access.</t>
+  </si>
+  <si>
+    <t>Login with empty credentials</t>
+  </si>
+  <si>
+    <t>1. Login page is accessible.</t>
+  </si>
+  <si>
+    <t>Required field validation messages should be displayed.</t>
+  </si>
+  <si>
+    <t>Logout functionality validation</t>
+  </si>
+  <si>
+    <t>User session should be terminated and dashboard access should be restricted post logout.</t>
+  </si>
+  <si>
+    <t>TC_3.1</t>
+  </si>
+  <si>
+    <t>Create note under Personal category</t>
+  </si>
+  <si>
+    <t>Note should be created successfully and visible only in Personal and All categories.</t>
+  </si>
+  <si>
+    <t>TC_3.2</t>
+  </si>
+  <si>
+    <t>Create note under Work category</t>
+  </si>
+  <si>
+    <t>Note should be created successfully and categorized correctly.</t>
+  </si>
+  <si>
+    <t>TC_3.3</t>
+  </si>
+  <si>
+    <t>Create note under Home category</t>
+  </si>
+  <si>
+    <t>TC_4.1</t>
+  </si>
+  <si>
+    <t>Edit note under Personal category</t>
+  </si>
+  <si>
+    <t>Title: Automation Updated</t>
+  </si>
+  <si>
+    <t>Note should update successfully without affecting category mapping.</t>
+  </si>
+  <si>
+    <t>TC_4.2</t>
+  </si>
+  <si>
+    <t>Edit note under Work category</t>
+  </si>
+  <si>
+    <t>Title: Work Task Updated</t>
+  </si>
+  <si>
+    <t>Note should reflect updated information correctly.</t>
+  </si>
+  <si>
+    <t>TC_4.3</t>
+  </si>
+  <si>
+    <t>Edit note under Home category</t>
+  </si>
+  <si>
+    <t>Title: Home Task Updated</t>
+  </si>
+  <si>
+    <t>Note should update successfully.</t>
+  </si>
+  <si>
+    <t>TC_5.1</t>
+  </si>
+  <si>
+    <t>Delete note from Personal category</t>
+  </si>
+  <si>
+    <t>Note should be permanently removed from Personal and All categories.</t>
+  </si>
+  <si>
+    <t>TC_5.2</t>
+  </si>
+  <si>
+    <t>Delete note from Work category</t>
+  </si>
+  <si>
+    <t>Note should be permanently removed from Work and All categories.</t>
+  </si>
+  <si>
+    <t>TC_5.3</t>
+  </si>
+  <si>
+    <t>Delete note from Home category</t>
+  </si>
+  <si>
+    <t>Note should be permanently removed from Home and All categories.</t>
+  </si>
+  <si>
+    <t>1. Browser is installed and operational.
+2. Registration page is accessible.
+3. Email is not already registered in the system.</t>
+  </si>
+  <si>
+    <t>1. Launch the browser.
+2. Navigate to the registration page URL.
+3. Verify registration page is displayed.
+4. Enter Name: Supreme Karki.
+5. Enter Email: supreme@yopmail.com.
+6. Enter Password: Admin@123.
+7. Click on Register button.
+8. Verify successful registration message.
+9. Verify user is redirected to Login page or Dashboard.</t>
+  </si>
+  <si>
+    <t>1. Browser is operational.
+2. Registration page is accessible.
+3. Email supreme@yopmail.com already exists in system.</t>
+  </si>
+  <si>
+    <t>1. Launch browser.
+2. Navigate to registration page.
+3. Enter Name: Supreme Karki.
+4. Enter Email: supreme@yopmail.com.
+5. Enter Password: Admin@123.
+6. Click Register.
+7. Verify error message is displayed.</t>
+  </si>
+  <si>
+    <t>1. Browser is operational.
+2. Registration page is accessible.</t>
+  </si>
+  <si>
+    <t>1. Launch browser.
+2. Navigate to registration page.
+3. Enter Name: Supreme Karki.
+4. Enter Email: abc@.
+5. Enter Password: Admin@123.
+6. Click Register.
+7. Verify validation message.</t>
+  </si>
+  <si>
+    <t>1. Launch browser.
+2. Navigate to registration page.
+3. Leave Name, Email, Password blank.
+4. Click Register.
+5. Verify validation messages.</t>
+  </si>
+  <si>
+    <t>1. User account exists.
+2. Login page is accessible.</t>
+  </si>
+  <si>
+    <t>1. Launch browser.
+2. Navigate to Login page.
+3. Enter Email: supreme@yopmail.com.
+4. Enter Password: Admin@123.
+5. Click Login.
+6. Verify dashboard is displayed.
+7. Verify Profile and Logout options are visible.</t>
+  </si>
+  <si>
+    <t>1. Launch browser.
+2. Navigate to Login page.
+3. Enter Email: wrong@yopmail.com.
+4. Enter Password: Admin@123.
+5. Click Login.
+6. Verify error message.</t>
+  </si>
+  <si>
+    <t>1. Launch browser.
+2. Navigate to Login page.
+3. Enter Email: supreme@yopmail.com.
+4. Enter Password: WrongPass123.
+5. Click Login.
+6. Verify error message.</t>
+  </si>
+  <si>
+    <t>1. Launch browser.
+2. Navigate to Login page.
+3. Leave Email and Password blank.
+4. Click Login.
+5. Verify validation messages.</t>
+  </si>
+  <si>
+    <t>1. User is logged in.
+2. Dashboard is accessible.</t>
+  </si>
+  <si>
+    <t>1. Click Logout.
+2. Verify redirection to Login page.
+3. Attempt to access dashboard URL directly.
+4. Verify access restriction.</t>
+  </si>
+  <si>
+    <t>1. Click Add Note.
+2. Select Category: Personal.
+3. Enter Title: Automation.
+4. Enter Description: Perform Automation Testing using Selenium.
+5. Click Save.
+6. Verify note under Personal and All categories only.</t>
+  </si>
+  <si>
+    <t>1. Click Add Note.
+2. Select Category: Work.
+3. Enter Title: Work Task.
+4. Enter Description: Perform Work Testing.
+5. Click Save.
+6. Verify note under Work and All categories only.</t>
+  </si>
+  <si>
+    <t>1. Click Add Note.
+2. Select Category: Home.
+3. Enter Title: Home Task.
+4. Enter Description: Perform Home Testing.
+5. Click Save.
+6. Verify note under Home and All categories only.</t>
+  </si>
+  <si>
+    <t>1. User is logged in.
+2. Note exists in Personal category.</t>
+  </si>
+  <si>
+    <t>1. Navigate to Personal category.
+2. Click Edit on note.
+3. Update Title and Description.
+4. Click Save.
+5. Verify updated details reflect correctly.</t>
+  </si>
+  <si>
+    <t>Title: Automation Updated
+Description: Perform Automation Testing using Cypress</t>
+  </si>
+  <si>
+    <t>1. User logged in.
+2. Note exists in Work category.</t>
+  </si>
+  <si>
+    <t>1. Navigate to Work category.
+2. Click Edit.
+3. Update details.
+4. Save changes.
+5. Verify update.</t>
+  </si>
+  <si>
+    <t>Title: Work Task Updated
+Description: Updated Work Testing</t>
+  </si>
+  <si>
+    <t>1. User logged in.
+2. Note exists in Home category.</t>
+  </si>
+  <si>
+    <t>1. Navigate to Home category.
+2. Click Edit.
+3. Update details.
+4. Save changes.
+5. Verify update.</t>
+  </si>
+  <si>
+    <t>Title: Home Task Updated
+Description: Updated Home Testing</t>
+  </si>
+  <si>
+    <t>1. User logged in.
+2. Note exists in Personal category.</t>
+  </si>
+  <si>
+    <t>1. Navigate to Personal.
+2. Click Delete.
+3. Confirm deletion.
+4. Verify note removal.</t>
+  </si>
+  <si>
+    <t>1. Navigate to Work.
+2. Click Delete.
+3. Confirm deletion.
+4. Verify note removal.</t>
+  </si>
+  <si>
+    <t>1. Navigate to Home.
+2. Click Delete.
+3. Confirm deletion.
+4. Verify note removal.</t>
   </si>
 </sst>
 </file>
@@ -1092,7 +1553,7 @@
         <v>55</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>37</v>
@@ -1121,7 +1582,7 @@
         <v>56</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>40</v>
@@ -1150,7 +1611,7 @@
         <v>57</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>23</v>
@@ -1179,7 +1640,7 @@
         <v>58</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>34</v>
@@ -1196,7 +1657,7 @@
     </row>
     <row r="11" spans="1:9" ht="145.80000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>59</v>
@@ -1208,7 +1669,7 @@
         <v>64</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>60</v>
@@ -1225,25 +1686,25 @@
     </row>
     <row r="12" spans="1:9" ht="132.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>64</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>12</v>
@@ -1252,27 +1713,27 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="145.80000000000001" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="132.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>64</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>12</v>
@@ -1283,22 +1744,22 @@
     </row>
     <row r="14" spans="1:9" ht="119.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>79</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>62</v>
@@ -1312,7 +1773,7 @@
     </row>
     <row r="15" spans="1:9" ht="119.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>59</v>
@@ -1324,7 +1785,7 @@
         <v>66</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>67</v>
@@ -1341,22 +1802,22 @@
     </row>
     <row r="16" spans="1:9" ht="119.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>62</v>
@@ -1370,25 +1831,25 @@
     </row>
     <row r="17" spans="1:27" ht="119.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>12</v>
@@ -1399,25 +1860,25 @@
     </row>
     <row r="18" spans="1:27" ht="106.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>66</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>12</v>
@@ -1446,25 +1907,25 @@
     </row>
     <row r="19" spans="1:27" ht="106.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>12</v>
@@ -1635,4 +2096,831 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="37.109375" customWidth="1"/>
+    <col min="5" max="5" width="40.5546875" customWidth="1"/>
+    <col min="6" max="6" width="25.88671875" customWidth="1"/>
+    <col min="7" max="7" width="18.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="132.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="93" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="93" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="93" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="106.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="93" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="93" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Z6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="18.33203125" customWidth="1"/>
+    <col min="4" max="4" width="23.109375" customWidth="1"/>
+    <col min="5" max="5" width="29.21875" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" customWidth="1"/>
+    <col min="7" max="7" width="23.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+    </row>
+    <row r="2" spans="1:26" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+    </row>
+    <row r="3" spans="1:26" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+    </row>
+    <row r="4" spans="1:26" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+    </row>
+    <row r="5" spans="1:26" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>